--- a/ValueSet-ACCESSCKMClinicalExclusionDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMClinicalExclusionDiagnosisVS.xlsx
@@ -157,7 +157,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMClinicalExclusionDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMClinicalExclusionDiagnosisVS.xlsx
@@ -127,7 +127,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -157,7 +157,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
